--- a/fixi_export.xlsx
+++ b/fixi_export.xlsx
@@ -16,6 +16,8 @@
     <sheet name="הזמנות" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="פרמטרי הזמנה אוטומטית" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="מלאי ומכרזים" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="תכנית שבועית" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="הזמנה יומית" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +49,10 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
     </font>
   </fonts>
   <fills count="4">
@@ -79,7 +85,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -88,6 +94,8 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -706,6 +714,650 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="80" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>תכנית הזמנות שבועית (ראשון-חמישי, 5 ימי עבודה)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>יום</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>תאריך</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>יום עבודה?</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>מספר פריטים</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>פריטים (רשימה)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>עלות משוערת</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ראשון</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>21</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>מזלג חד פעמי, מפית נייר, סכין חד פעמי, בצל (2321 gram), גבינה צהובה (2361 gram), חזה עוף פרוס (12228 gram), חסה (10210 gram), לחמניית המבורגר (110 unit), מלפפון חמוץ (2532 gram), עגבנייה (6099 gram), פירורי לחם, פרמזן מגוררת, קציצת בקר 180 גרם (56 unit), קרוטונים, רוטב המבורגר, רוטב קיסר, שמן טיגון, מכסה לקופסת סלט, קופסת המבורגר קרטון, קופסת סלט PET, שקית נייר ניידים</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>2022.44</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>שני</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>שלישי</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>חזה עוף פרוס (12228 gram), חסה (10210 gram), לחמניית המבורגר (110 unit), עגבנייה (6099 gram), קציצת בקר 180 גרם (56 unit)</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>1747.01</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>רביעי</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>בצל (3366 gram), גבינה צהובה (3507 gram), רוטב המבורגר (1471 ml), רוטב קיסר (566 ml)</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>380.97</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>חמישי</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>חזה עוף פרוס (19485 gram), חסה (15998 gram), לחמניית המבורגר (186 unit), עגבנייה (10096 gram), קציצת בקר 180 גרם (101 unit)</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>2921.69</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>יום סגור</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>לא</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>יום סגור</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="35" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>הזמנה יומית מומלצת - 2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>רכיב</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>אב מוצר</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>קטגוריה</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>יחידה</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>מלאי נוכחי</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>שימוש יומי</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>פחת %</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>מחזור הזמנה</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>כיסוי יעד</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>כמות מוצעת</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>מחיר/יח'</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>עלות</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>סיבה</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>חזה עוף פרוס</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>53083.8</v>
+      </c>
+      <c r="F4" t="n">
+        <v>6894</v>
+      </c>
+      <c r="G4" t="n">
+        <v>5</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>sun,tue,thu</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>19484.62</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1071.65</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>מחזור sun,tue,thu - כיסוי 10 ימים</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>קציצת בקר 180 גרם</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>המבורגר</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>490.99</v>
+      </c>
+      <c r="F5" t="n">
+        <v>44.43</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>sun,tue,thu</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>101.45</v>
+      </c>
+      <c r="K5" t="n">
+        <v>9</v>
+      </c>
+      <c r="L5" t="n">
+        <v>913.09</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>מחזור sun,tue,thu - כיסוי 13 ימים</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>לחמניית המבורגר</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>המבורגר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>572.62</v>
+      </c>
+      <c r="F6" t="n">
+        <v>74.37</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>sun,tue,thu</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>186.22</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>465.56</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>מחזור sun,tue,thu - כיסוי 10 ימים</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>חסה</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>30305.33</v>
+      </c>
+      <c r="F7" t="n">
+        <v>5093.33</v>
+      </c>
+      <c r="G7" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>sun,tue,thu</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15997.7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L7" t="n">
+        <v>319.95</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>מחזור sun,tue,thu - כיסוי 8 ימים</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>עגבנייה</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>21878.15</v>
+      </c>
+      <c r="F8" t="n">
+        <v>3677</v>
+      </c>
+      <c r="G8" t="n">
+        <v>8</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>sun,tue,thu</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>10095.76</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L8" t="n">
+        <v>151.44</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>מחזור sun,tue,thu - כיסוי 8 ימים</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n"/>
+      <c r="C9" s="7" t="n"/>
+      <c r="D9" s="7" t="n"/>
+      <c r="E9" s="7" t="n"/>
+      <c r="F9" s="7" t="n"/>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="7" t="n"/>
+      <c r="I9" s="7" t="n"/>
+      <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
+      <c r="L9" s="5" t="n">
+        <v>2921.69</v>
+      </c>
+      <c r="M9" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -862,17 +1514,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:L22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -888,32 +1544,52 @@
       </c>
       <c r="C1" s="4" t="inlineStr">
         <is>
+          <t>אב מוצר</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
           <t>קטגוריה</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>יחידה</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>מחיר ליחידה</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>פחת %</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>מלאי נוכחי</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>סף הזמנה</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>זמן אספקה (ימים)</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>כיסוי ימים (יעד)</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>מחזור הזמנה</t>
         </is>
       </c>
     </row>
@@ -928,25 +1604,41 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t>disposable</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.15</v>
       </c>
-      <c r="F2" t="n">
-        <v>386146</v>
-      </c>
       <c r="G2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" t="n">
+        <v>899.64</v>
+      </c>
+      <c r="I2" t="n">
         <v>300</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>14</v>
+      </c>
+      <c r="K2" t="n">
+        <v>14</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -960,25 +1652,41 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>disposable</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.05</v>
       </c>
-      <c r="F3" t="n">
-        <v>1430272</v>
-      </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4493.44</v>
+      </c>
+      <c r="I3" t="n">
         <v>1000</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>14</v>
+      </c>
+      <c r="K3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -992,25 +1700,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>disposable</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.15</v>
       </c>
-      <c r="F4" t="n">
-        <v>386146</v>
-      </c>
       <c r="G4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H4" t="n">
+        <v>899.64</v>
+      </c>
+      <c r="I4" t="n">
         <v>300</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>14</v>
+      </c>
+      <c r="K4" t="n">
+        <v>14</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1024,25 +1748,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>המבורגר</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.01</v>
       </c>
-      <c r="F5" t="n">
-        <v>1175100</v>
-      </c>
       <c r="G5" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6042.93</v>
+      </c>
+      <c r="I5" t="n">
         <v>1000</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>5</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>sun,wed</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1056,25 +1796,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>המבורגר</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.08</v>
       </c>
-      <c r="F6" t="n">
-        <v>3593875</v>
-      </c>
       <c r="G6" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>17106.83</v>
+      </c>
+      <c r="I6" t="n">
         <v>3000</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>14</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>sun,wed</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1088,25 +1844,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.055</v>
       </c>
-      <c r="F7" t="n">
-        <v>425730</v>
-      </c>
       <c r="G7" t="n">
+        <v>5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>53083.8</v>
+      </c>
+      <c r="I7" t="n">
         <v>2500</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>sun,tue,thu</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -1120,25 +1892,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>0.02</v>
       </c>
-      <c r="F8" t="n">
-        <v>136960</v>
-      </c>
       <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="n">
+        <v>30305.33</v>
+      </c>
+      <c r="I8" t="n">
         <v>1500</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>sun,tue,thu</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1152,25 +1940,41 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>המבורגר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>2.5</v>
       </c>
-      <c r="F9" t="n">
-        <v>72422</v>
-      </c>
       <c r="G9" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" t="n">
+        <v>572.62</v>
+      </c>
+      <c r="I9" t="n">
         <v>80</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>sun,tue,thu</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1184,25 +1988,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>המבורגר</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>0.025</v>
       </c>
-      <c r="F10" t="n">
-        <v>756325</v>
-      </c>
       <c r="G10" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>11897.02</v>
+      </c>
+      <c r="I10" t="n">
         <v>800</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>14</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -1216,25 +2036,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0.015</v>
       </c>
-      <c r="F11" t="n">
-        <v>1145910</v>
-      </c>
       <c r="G11" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" t="n">
+        <v>21878.15</v>
+      </c>
+      <c r="I11" t="n">
         <v>2000</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>sun,tue,thu</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1248,25 +2084,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>0.012</v>
       </c>
-      <c r="F12" t="n">
-        <v>1546680</v>
-      </c>
       <c r="G12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>28496.53</v>
+      </c>
+      <c r="I12" t="n">
         <v>1500</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>14</v>
+      </c>
+      <c r="K12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1280,25 +2132,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>סלט קיסר</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>0.12</v>
       </c>
-      <c r="F13" t="n">
-        <v>640710</v>
-      </c>
       <c r="G13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>8939.879999999999</v>
+      </c>
+      <c r="I13" t="n">
         <v>500</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>21</v>
+      </c>
+      <c r="K13" t="n">
+        <v>14</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1312,25 +2180,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
+          <t>המבורגר</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>9</v>
       </c>
-      <c r="F14" t="n">
-        <v>58755</v>
-      </c>
       <c r="G14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H14" t="n">
+        <v>490.99</v>
+      </c>
+      <c r="I14" t="n">
         <v>60</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>10</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>sun,tue,thu</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1344,25 +2228,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>סלט קיסר</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>0.03</v>
       </c>
-      <c r="F15" t="n">
-        <v>567850</v>
-      </c>
       <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="n">
+        <v>14899.79</v>
+      </c>
+      <c r="I15" t="n">
         <v>500</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>21</v>
+      </c>
+      <c r="K15" t="n">
+        <v>14</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1376,25 +2276,41 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
+          <t>המבורגר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>0.03</v>
       </c>
-      <c r="F16" t="n">
-        <v>729325</v>
-      </c>
       <c r="G16" t="n">
+        <v>3</v>
+      </c>
+      <c r="H16" t="n">
+        <v>37151.8</v>
+      </c>
+      <c r="I16" t="n">
         <v>1000</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>14</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>sun,wed</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1408,25 +2324,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>סלט קיסר</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>0.04</v>
       </c>
-      <c r="F17" t="n">
-        <v>708560</v>
-      </c>
       <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>14303.8</v>
+      </c>
+      <c r="I17" t="n">
         <v>800</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>14</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>sun,wed</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1440,25 +2372,41 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>0.018</v>
       </c>
-      <c r="F18" t="n">
-        <v>4320020</v>
-      </c>
       <c r="G18" t="n">
+        <v>8</v>
+      </c>
+      <c r="H18" t="n">
+        <v>42744.8</v>
+      </c>
+      <c r="I18" t="n">
         <v>4000</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>14</v>
+      </c>
+      <c r="K18" t="n">
+        <v>14</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1472,25 +2420,41 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
+          <t>סלט קיסר (TA)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
           <t>packaging</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>0.4</v>
       </c>
-      <c r="F19" t="n">
-        <v>147090</v>
-      </c>
       <c r="G19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H19" t="n">
+        <v>191.19</v>
+      </c>
+      <c r="I19" t="n">
         <v>120</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>14</v>
+      </c>
+      <c r="K19" t="n">
+        <v>14</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1504,25 +2468,41 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>המבורגר (TA), קריספי ציקן (TA)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>packaging</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>1.2</v>
       </c>
-      <c r="F20" t="n">
-        <v>189056</v>
-      </c>
       <c r="G20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>708.45</v>
+      </c>
+      <c r="I20" t="n">
         <v>150</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>14</v>
+      </c>
+      <c r="K20" t="n">
+        <v>14</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1536,25 +2516,41 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>סלט קיסר (TA)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>packaging</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>1.5</v>
       </c>
-      <c r="F21" t="n">
-        <v>147090</v>
-      </c>
       <c r="G21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H21" t="n">
+        <v>191.19</v>
+      </c>
+      <c r="I21" t="n">
         <v>120</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>14</v>
+      </c>
+      <c r="K21" t="n">
+        <v>14</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1568,25 +2564,41 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>packaging</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>0.7</v>
       </c>
-      <c r="F22" t="n">
-        <v>236146</v>
-      </c>
       <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>899.64</v>
+      </c>
+      <c r="I22" t="n">
         <v>200</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>14</v>
+      </c>
+      <c r="K22" t="n">
+        <v>14</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -76302,20 +77314,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -76326,50 +77342,70 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
+          <t>אב מוצר</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
           <t>יחידה</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>פחת %</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>צריכה שנתית</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>ממוצע חודשי</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>ממוצע יומי</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>זמן אספקה (ימים)</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>כיסוי יעד (ימים)</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>מלאי ביטחון</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Reorder Point</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>כמות הזמנה מומלצת</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>כמות הזמנה (ללא פחת)</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>כמות מוצעת (כולל פחת)</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>מחיר/יח'</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>עלות הזמנה</t>
         </is>
@@ -76383,35 +77419,49 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
         <v>2574270</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>214522.5</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>7052.79</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>7</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="n">
         <v>64356.8</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>113726.3</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>214522.5</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
+        <v>225813.2</v>
+      </c>
+      <c r="N2" t="n">
         <v>0.055</v>
       </c>
-      <c r="K2" t="n">
-        <v>11798.74</v>
+      <c r="O2" t="n">
+        <v>12419.72</v>
       </c>
     </row>
     <row r="3">
@@ -76422,35 +77472,49 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
+        <v>12</v>
+      </c>
+      <c r="E3" t="n">
         <v>1863040</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>155253.3</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>5104.22</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>5</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
         <v>46576</v>
       </c>
-      <c r="H3" t="n">
+      <c r="K3" t="n">
         <v>72097.10000000001</v>
       </c>
-      <c r="I3" t="n">
+      <c r="L3" t="n">
         <v>155253.3</v>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
+        <v>176424.2</v>
+      </c>
+      <c r="N3" t="n">
         <v>0.02</v>
       </c>
-      <c r="K3" t="n">
-        <v>3105.07</v>
+      <c r="O3" t="n">
+        <v>3528.48</v>
       </c>
     </row>
     <row r="4">
@@ -76461,35 +77525,49 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
+        <v>8</v>
+      </c>
+      <c r="E4" t="n">
         <v>1354090</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>112840.8</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>3709.84</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>5</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
         <v>33852.2</v>
       </c>
-      <c r="H4" t="n">
+      <c r="K4" t="n">
         <v>52401.4</v>
       </c>
-      <c r="I4" t="n">
+      <c r="L4" t="n">
         <v>112840.8</v>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
+        <v>122653.1</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.015</v>
       </c>
-      <c r="K4" t="n">
-        <v>1692.61</v>
+      <c r="O4" t="n">
+        <v>1839.8</v>
       </c>
     </row>
     <row r="5">
@@ -76500,35 +77578,49 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>המבורגר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
         <v>770675</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>64222.9</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>2111.44</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>14</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" t="n">
         <v>19266.9</v>
       </c>
-      <c r="H5" t="n">
+      <c r="K5" t="n">
         <v>48827</v>
       </c>
-      <c r="I5" t="n">
+      <c r="L5" t="n">
         <v>64222.9</v>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
+        <v>66209.2</v>
+      </c>
+      <c r="N5" t="n">
         <v>0.03</v>
       </c>
-      <c r="K5" t="n">
-        <v>1926.69</v>
+      <c r="O5" t="n">
+        <v>1986.28</v>
       </c>
     </row>
     <row r="6">
@@ -76539,35 +77631,49 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
+        <v>8</v>
+      </c>
+      <c r="E6" t="n">
         <v>679980</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>56665</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>1862.96</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>14</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
+        <v>14</v>
+      </c>
+      <c r="J6" t="n">
         <v>16999.5</v>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>43080.9</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>56665</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
+        <v>61592.4</v>
+      </c>
+      <c r="N6" t="n">
         <v>0.018</v>
       </c>
-      <c r="K6" t="n">
-        <v>1019.97</v>
+      <c r="O6" t="n">
+        <v>1108.66</v>
       </c>
     </row>
     <row r="7">
@@ -76578,35 +77684,49 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E7" t="n">
         <v>453320</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>37776.7</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>1241.97</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>14</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
+        <v>14</v>
+      </c>
+      <c r="J7" t="n">
         <v>11333</v>
       </c>
-      <c r="H7" t="n">
+      <c r="K7" t="n">
         <v>28720.6</v>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>37776.7</v>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
+        <v>38351.9</v>
+      </c>
+      <c r="N7" t="n">
         <v>0.012</v>
       </c>
-      <c r="K7" t="n">
-        <v>453.32</v>
+      <c r="O7" t="n">
+        <v>460.22</v>
       </c>
     </row>
     <row r="8">
@@ -76617,35 +77737,49 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>המבורגר</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
         <v>406125</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>33843.8</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>1112.67</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>14</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="n">
         <v>10153.1</v>
       </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
         <v>25730.5</v>
       </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
         <v>33843.8</v>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
+        <v>34890.5</v>
+      </c>
+      <c r="N8" t="n">
         <v>0.08</v>
       </c>
-      <c r="K8" t="n">
-        <v>2707.5</v>
+      <c r="O8" t="n">
+        <v>2791.24</v>
       </c>
     </row>
     <row r="9">
@@ -76656,35 +77790,49 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>המבורגר</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E9" t="n">
         <v>324900</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>27075</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>890.14</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>5</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
         <v>8122.5</v>
       </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
         <v>12573.2</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>27075</v>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
+        <v>31852.9</v>
+      </c>
+      <c r="N9" t="n">
         <v>0.01</v>
       </c>
-      <c r="K9" t="n">
-        <v>270.75</v>
+      <c r="O9" t="n">
+        <v>318.53</v>
       </c>
     </row>
     <row r="10">
@@ -76695,35 +77843,49 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>סלט קיסר</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
         <v>291440</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>24286.7</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>798.47</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>14</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="n">
         <v>7286</v>
       </c>
-      <c r="H10" t="n">
+      <c r="K10" t="n">
         <v>18464.5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="L10" t="n">
         <v>24286.7</v>
       </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
+        <v>25037.8</v>
+      </c>
+      <c r="N10" t="n">
         <v>0.04</v>
       </c>
-      <c r="K10" t="n">
-        <v>971.47</v>
+      <c r="O10" t="n">
+        <v>1001.51</v>
       </c>
     </row>
     <row r="11">
@@ -76734,35 +77896,49 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>המבורגר</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
         <v>243675</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>20306.2</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>667.6</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>14</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" t="n">
         <v>6091.9</v>
       </c>
-      <c r="H11" t="n">
+      <c r="K11" t="n">
         <v>15438.3</v>
       </c>
-      <c r="I11" t="n">
+      <c r="L11" t="n">
         <v>20306.2</v>
       </c>
-      <c r="J11" t="n">
+      <c r="M11" t="n">
+        <v>20934.3</v>
+      </c>
+      <c r="N11" t="n">
         <v>0.025</v>
       </c>
-      <c r="K11" t="n">
-        <v>507.66</v>
+      <c r="O11" t="n">
+        <v>523.36</v>
       </c>
     </row>
     <row r="12">
@@ -76773,35 +77949,49 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>סלט קיסר</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" t="n">
         <v>182150</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>15179.2</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>499.04</v>
       </c>
-      <c r="F12" t="n">
+      <c r="H12" t="n">
         <v>21</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J12" t="n">
         <v>4553.8</v>
       </c>
-      <c r="H12" t="n">
+      <c r="K12" t="n">
         <v>15033.6</v>
       </c>
-      <c r="I12" t="n">
+      <c r="L12" t="n">
         <v>15179.2</v>
       </c>
-      <c r="J12" t="n">
+      <c r="M12" t="n">
+        <v>15488.9</v>
+      </c>
+      <c r="N12" t="n">
         <v>0.03</v>
       </c>
-      <c r="K12" t="n">
-        <v>455.37</v>
+      <c r="O12" t="n">
+        <v>464.67</v>
       </c>
     </row>
     <row r="13">
@@ -76812,35 +78002,49 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>סלט קיסר</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E13" t="n">
         <v>109290</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>9107.5</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>299.42</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
         <v>21</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
+        <v>14</v>
+      </c>
+      <c r="J13" t="n">
         <v>2732.2</v>
       </c>
-      <c r="H13" t="n">
+      <c r="K13" t="n">
         <v>9020.200000000001</v>
       </c>
-      <c r="I13" t="n">
+      <c r="L13" t="n">
         <v>9107.5</v>
       </c>
-      <c r="J13" t="n">
+      <c r="M13" t="n">
+        <v>9341</v>
+      </c>
+      <c r="N13" t="n">
         <v>0.12</v>
       </c>
-      <c r="K13" t="n">
-        <v>1092.9</v>
+      <c r="O13" t="n">
+        <v>1120.92</v>
       </c>
     </row>
     <row r="14">
@@ -76851,35 +78055,49 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
         <v>69728</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>5810.7</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>191.04</v>
       </c>
-      <c r="F14" t="n">
+      <c r="H14" t="n">
         <v>14</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
+        <v>14</v>
+      </c>
+      <c r="J14" t="n">
         <v>1743.2</v>
       </c>
-      <c r="H14" t="n">
+      <c r="K14" t="n">
         <v>4417.7</v>
       </c>
-      <c r="I14" t="n">
+      <c r="L14" t="n">
         <v>5810.7</v>
       </c>
-      <c r="J14" t="n">
+      <c r="M14" t="n">
+        <v>5869.4</v>
+      </c>
+      <c r="N14" t="n">
         <v>0.05</v>
       </c>
-      <c r="K14" t="n">
-        <v>290.53</v>
+      <c r="O14" t="n">
+        <v>293.47</v>
       </c>
     </row>
     <row r="15">
@@ -76890,35 +78108,49 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>המבורגר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" t="n">
         <v>27578</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>2298.2</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>75.56</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>7</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
         <v>689.4</v>
       </c>
-      <c r="H15" t="n">
+      <c r="K15" t="n">
         <v>1218.3</v>
       </c>
-      <c r="I15" t="n">
+      <c r="L15" t="n">
         <v>2298.2</v>
       </c>
-      <c r="J15" t="n">
+      <c r="M15" t="n">
+        <v>2345.1</v>
+      </c>
+      <c r="N15" t="n">
         <v>2.5</v>
       </c>
-      <c r="K15" t="n">
-        <v>5745.42</v>
+      <c r="O15" t="n">
+        <v>5862.67</v>
       </c>
     </row>
     <row r="16">
@@ -76929,35 +78161,49 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>המבורגר</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E16" t="n">
         <v>16245</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>1353.8</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>44.51</v>
       </c>
-      <c r="F16" t="n">
+      <c r="H16" t="n">
         <v>10</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" t="n">
         <v>406.1</v>
       </c>
-      <c r="H16" t="n">
+      <c r="K16" t="n">
         <v>851.2</v>
       </c>
-      <c r="I16" t="n">
+      <c r="L16" t="n">
         <v>1353.8</v>
       </c>
-      <c r="J16" t="n">
+      <c r="M16" t="n">
+        <v>1388.5</v>
+      </c>
+      <c r="N16" t="n">
         <v>9</v>
       </c>
-      <c r="K16" t="n">
-        <v>12183.75</v>
+      <c r="O16" t="n">
+        <v>12496.15</v>
       </c>
     </row>
     <row r="17">
@@ -76968,35 +78214,49 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
         <v>13854</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>1154.5</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>37.96</v>
       </c>
-      <c r="F17" t="n">
+      <c r="H17" t="n">
         <v>14</v>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
+        <v>14</v>
+      </c>
+      <c r="J17" t="n">
         <v>346.3</v>
       </c>
-      <c r="H17" t="n">
+      <c r="K17" t="n">
         <v>877.7</v>
       </c>
-      <c r="I17" t="n">
+      <c r="L17" t="n">
         <v>1154.5</v>
       </c>
-      <c r="J17" t="n">
+      <c r="M17" t="n">
+        <v>1166.2</v>
+      </c>
+      <c r="N17" t="n">
         <v>0.7</v>
       </c>
-      <c r="K17" t="n">
-        <v>808.15</v>
+      <c r="O17" t="n">
+        <v>816.3099999999999</v>
       </c>
     </row>
     <row r="18">
@@ -77007,35 +78267,49 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E18" t="n">
         <v>13854</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>1154.5</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>37.96</v>
       </c>
-      <c r="F18" t="n">
+      <c r="H18" t="n">
         <v>14</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
+        <v>14</v>
+      </c>
+      <c r="J18" t="n">
         <v>346.3</v>
       </c>
-      <c r="H18" t="n">
+      <c r="K18" t="n">
         <v>877.7</v>
       </c>
-      <c r="I18" t="n">
+      <c r="L18" t="n">
         <v>1154.5</v>
       </c>
-      <c r="J18" t="n">
+      <c r="M18" t="n">
+        <v>1160.3</v>
+      </c>
+      <c r="N18" t="n">
         <v>0.15</v>
       </c>
-      <c r="K18" t="n">
-        <v>173.17</v>
+      <c r="O18" t="n">
+        <v>174.05</v>
       </c>
     </row>
     <row r="19">
@@ -77046,35 +78320,49 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E19" t="n">
         <v>13854</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>1154.5</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>37.96</v>
       </c>
-      <c r="F19" t="n">
+      <c r="H19" t="n">
         <v>14</v>
       </c>
-      <c r="G19" t="n">
+      <c r="I19" t="n">
+        <v>14</v>
+      </c>
+      <c r="J19" t="n">
         <v>346.3</v>
       </c>
-      <c r="H19" t="n">
+      <c r="K19" t="n">
         <v>877.7</v>
       </c>
-      <c r="I19" t="n">
+      <c r="L19" t="n">
         <v>1154.5</v>
       </c>
-      <c r="J19" t="n">
+      <c r="M19" t="n">
+        <v>1160.3</v>
+      </c>
+      <c r="N19" t="n">
         <v>0.15</v>
       </c>
-      <c r="K19" t="n">
-        <v>173.17</v>
+      <c r="O19" t="n">
+        <v>174.05</v>
       </c>
     </row>
     <row r="20">
@@ -77085,35 +78373,49 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>המבורגר (TA), קריספי ציקן (TA)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E20" t="n">
         <v>10944</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>912</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>29.98</v>
       </c>
-      <c r="F20" t="n">
+      <c r="H20" t="n">
         <v>14</v>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
+        <v>14</v>
+      </c>
+      <c r="J20" t="n">
         <v>273.6</v>
       </c>
-      <c r="H20" t="n">
+      <c r="K20" t="n">
         <v>693.4</v>
       </c>
-      <c r="I20" t="n">
+      <c r="L20" t="n">
         <v>912</v>
       </c>
-      <c r="J20" t="n">
+      <c r="M20" t="n">
+        <v>925.9</v>
+      </c>
+      <c r="N20" t="n">
         <v>1.2</v>
       </c>
-      <c r="K20" t="n">
-        <v>1094.4</v>
+      <c r="O20" t="n">
+        <v>1111.07</v>
       </c>
     </row>
     <row r="21">
@@ -77124,35 +78426,49 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>סלט קיסר (TA)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E21" t="n">
         <v>2910</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>242.5</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>7.97</v>
       </c>
-      <c r="F21" t="n">
+      <c r="H21" t="n">
         <v>14</v>
       </c>
-      <c r="G21" t="n">
+      <c r="I21" t="n">
+        <v>14</v>
+      </c>
+      <c r="J21" t="n">
         <v>72.8</v>
       </c>
-      <c r="H21" t="n">
+      <c r="K21" t="n">
         <v>184.4</v>
       </c>
-      <c r="I21" t="n">
+      <c r="L21" t="n">
         <v>242.5</v>
       </c>
-      <c r="J21" t="n">
+      <c r="M21" t="n">
+        <v>246.2</v>
+      </c>
+      <c r="N21" t="n">
         <v>1.5</v>
       </c>
-      <c r="K21" t="n">
-        <v>363.75</v>
+      <c r="O21" t="n">
+        <v>369.29</v>
       </c>
     </row>
     <row r="22">
@@ -77163,35 +78479,49 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>סלט קיסר (TA)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E22" t="n">
         <v>2910</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>242.5</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>7.97</v>
       </c>
-      <c r="F22" t="n">
+      <c r="H22" t="n">
         <v>14</v>
       </c>
-      <c r="G22" t="n">
+      <c r="I22" t="n">
+        <v>14</v>
+      </c>
+      <c r="J22" t="n">
         <v>72.8</v>
       </c>
-      <c r="H22" t="n">
+      <c r="K22" t="n">
         <v>184.4</v>
       </c>
-      <c r="I22" t="n">
+      <c r="L22" t="n">
         <v>242.5</v>
       </c>
-      <c r="J22" t="n">
+      <c r="M22" t="n">
+        <v>246.2</v>
+      </c>
+      <c r="N22" t="n">
         <v>0.4</v>
       </c>
-      <c r="K22" t="n">
-        <v>97</v>
+      <c r="O22" t="n">
+        <v>98.48</v>
       </c>
     </row>
   </sheetData>
@@ -77205,20 +78535,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -77229,50 +78562,65 @@
       </c>
       <c r="B1" s="4" t="inlineStr">
         <is>
+          <t>אב מוצר</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
           <t>קטגוריה</t>
         </is>
       </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>יחידה</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>פחת %</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>מלאי נוכחי</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>סף הזמנה</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>מחזור הזמנה</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>שימוש 30 יום</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>שימוש יומי</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>ימים שנשארו</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>דרוש מכרז?</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>כמות מוצעת למכרז</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>עלות מוערכת</t>
         </is>
@@ -77286,38 +78634,51 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>disposable</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>386146</v>
-      </c>
       <c r="E2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F2" t="n">
+        <v>899.64</v>
+      </c>
+      <c r="G2" t="n">
         <v>300</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>1134</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>37.8</v>
       </c>
-      <c r="H2" t="n">
-        <v>10215.5</v>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="L2" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77329,38 +78690,51 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>disposable</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>1430272</v>
-      </c>
       <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4493.44</v>
+      </c>
+      <c r="G3" t="n">
         <v>1000</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
         <v>5664</v>
       </c>
-      <c r="G3" t="n">
+      <c r="J3" t="n">
         <v>188.8</v>
       </c>
-      <c r="H3" t="n">
-        <v>7575.6</v>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="L3" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>0</v>
       </c>
-      <c r="K3" t="n">
+      <c r="N3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77372,38 +78746,51 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>disposable</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D4" t="n">
-        <v>386146</v>
-      </c>
       <c r="E4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>899.64</v>
+      </c>
+      <c r="G4" t="n">
         <v>300</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
         <v>1134</v>
       </c>
-      <c r="G4" t="n">
+      <c r="J4" t="n">
         <v>37.8</v>
       </c>
-      <c r="H4" t="n">
-        <v>10215.5</v>
-      </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="K4" t="n">
+      <c r="N4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77415,38 +78802,51 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>המבורגר</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>1175100</v>
-      </c>
       <c r="E5" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" t="n">
+        <v>6042.93</v>
+      </c>
+      <c r="G5" t="n">
         <v>1000</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>sun,wed</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>26660</v>
       </c>
-      <c r="G5" t="n">
+      <c r="J5" t="n">
         <v>888.67</v>
       </c>
-      <c r="H5" t="n">
-        <v>1322.3</v>
-      </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="M5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77458,38 +78858,51 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>המבורגר</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>3593875</v>
-      </c>
       <c r="E6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" t="n">
+        <v>17106.83</v>
+      </c>
+      <c r="G6" t="n">
         <v>3000</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>sun,wed</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
         <v>33325</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>1110.83</v>
       </c>
-      <c r="H6" t="n">
-        <v>3235.3</v>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>0</v>
       </c>
-      <c r="K6" t="n">
+      <c r="N6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77501,38 +78914,51 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>425730</v>
-      </c>
       <c r="E7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>53083.8</v>
+      </c>
+      <c r="G7" t="n">
         <v>2500</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>sun,tue,thu</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
         <v>206820</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>6894</v>
       </c>
-      <c r="H7" t="n">
-        <v>61.8</v>
-      </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
         <v>0</v>
       </c>
-      <c r="K7" t="n">
+      <c r="N7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77544,38 +78970,51 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="D8" t="n">
-        <v>136960</v>
-      </c>
       <c r="E8" t="n">
+        <v>12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>30305.33</v>
+      </c>
+      <c r="G8" t="n">
         <v>1500</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>sun,tue,thu</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
         <v>152800</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>5093.33</v>
       </c>
-      <c r="H8" t="n">
-        <v>26.9</v>
-      </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L8" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
+      <c r="N8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77587,38 +79026,51 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>המבורגר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D9" t="n">
-        <v>72422</v>
-      </c>
       <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>572.62</v>
+      </c>
+      <c r="G9" t="n">
         <v>80</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>sun,tue,thu</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
         <v>2231</v>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>74.37</v>
       </c>
-      <c r="H9" t="n">
-        <v>973.9</v>
-      </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="L9" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>0</v>
       </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77630,38 +79082,51 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>המבורגר</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="D10" t="n">
-        <v>756325</v>
-      </c>
       <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>11897.02</v>
+      </c>
+      <c r="G10" t="n">
         <v>800</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
         <v>19995</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>666.5</v>
       </c>
-      <c r="H10" t="n">
-        <v>1134.8</v>
-      </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L10" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
         <v>0</v>
       </c>
-      <c r="K10" t="n">
+      <c r="N10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77673,38 +79138,51 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>1145910</v>
-      </c>
       <c r="E11" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" t="n">
+        <v>21878.15</v>
+      </c>
+      <c r="G11" t="n">
         <v>2000</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>sun,tue,thu</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
         <v>110310</v>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>3677</v>
       </c>
-      <c r="H11" t="n">
-        <v>311.6</v>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="M11" t="n">
         <v>0</v>
       </c>
-      <c r="K11" t="n">
+      <c r="N11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77716,38 +79194,51 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
+          <t>קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="D12" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>1546680</v>
-      </c>
       <c r="E12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>28496.53</v>
+      </c>
+      <c r="G12" t="n">
         <v>1500</v>
       </c>
-      <c r="F12" t="n">
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
         <v>35920</v>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
         <v>1197.33</v>
       </c>
-      <c r="H12" t="n">
-        <v>1291.8</v>
-      </c>
-      <c r="I12" t="inlineStr">
+      <c r="K12" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="L12" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="M12" t="n">
         <v>0</v>
       </c>
-      <c r="K12" t="n">
+      <c r="N12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77759,38 +79250,51 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
+          <t>סלט קיסר</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>640710</v>
-      </c>
       <c r="E13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F13" t="n">
+        <v>8939.879999999999</v>
+      </c>
+      <c r="G13" t="n">
         <v>500</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
         <v>9015</v>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>300.5</v>
       </c>
-      <c r="H13" t="n">
-        <v>2132.1</v>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="K13" t="n">
+        <v>29.8</v>
+      </c>
+      <c r="L13" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="M13" t="n">
         <v>0</v>
       </c>
-      <c r="K13" t="n">
+      <c r="N13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77802,38 +79306,51 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
+          <t>המבורגר</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>58755</v>
-      </c>
       <c r="E14" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F14" t="n">
+        <v>490.99</v>
+      </c>
+      <c r="G14" t="n">
         <v>60</v>
       </c>
-      <c r="F14" t="n">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>sun,tue,thu</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
         <v>1333</v>
       </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
         <v>44.43</v>
       </c>
-      <c r="H14" t="n">
-        <v>1322.3</v>
-      </c>
-      <c r="I14" t="inlineStr">
+      <c r="K14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="L14" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="M14" t="n">
         <v>0</v>
       </c>
-      <c r="K14" t="n">
+      <c r="N14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77845,38 +79362,51 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
+          <t>סלט קיסר</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>gram</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>567850</v>
-      </c>
       <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="n">
+        <v>14899.79</v>
+      </c>
+      <c r="G15" t="n">
         <v>500</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
         <v>15025</v>
       </c>
-      <c r="G15" t="n">
+      <c r="J15" t="n">
         <v>500.83</v>
       </c>
-      <c r="H15" t="n">
-        <v>1133.8</v>
-      </c>
-      <c r="I15" t="inlineStr">
+      <c r="K15" t="n">
+        <v>29.7</v>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="n">
+      <c r="N15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77888,38 +79418,51 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>המבורגר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>729325</v>
-      </c>
       <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>37151.8</v>
+      </c>
+      <c r="G16" t="n">
         <v>1000</v>
       </c>
-      <c r="F16" t="n">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>sun,wed</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
         <v>62440</v>
       </c>
-      <c r="G16" t="n">
+      <c r="J16" t="n">
         <v>2081.33</v>
       </c>
-      <c r="H16" t="n">
-        <v>350.4</v>
-      </c>
-      <c r="I16" t="inlineStr">
+      <c r="K16" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="L16" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="K16" t="n">
+      <c r="N16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77931,38 +79474,51 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>סלט קיסר</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="D17" t="n">
-        <v>708560</v>
-      </c>
       <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>14303.8</v>
+      </c>
+      <c r="G17" t="n">
         <v>800</v>
       </c>
-      <c r="F17" t="n">
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>sun,wed</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
         <v>24040</v>
       </c>
-      <c r="G17" t="n">
+      <c r="J17" t="n">
         <v>801.33</v>
       </c>
-      <c r="H17" t="n">
-        <v>884.2</v>
-      </c>
-      <c r="I17" t="inlineStr">
+      <c r="K17" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="L17" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="n">
+      <c r="N17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77974,38 +79530,51 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>food</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>ml</t>
         </is>
       </c>
-      <c r="D18" t="n">
-        <v>4320020</v>
-      </c>
       <c r="E18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42744.8</v>
+      </c>
+      <c r="G18" t="n">
         <v>4000</v>
       </c>
-      <c r="F18" t="n">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
         <v>53880</v>
       </c>
-      <c r="G18" t="n">
+      <c r="J18" t="n">
         <v>1796</v>
       </c>
-      <c r="H18" t="n">
-        <v>2405.4</v>
-      </c>
-      <c r="I18" t="inlineStr">
+      <c r="K18" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="K18" t="n">
+      <c r="N18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -78017,38 +79586,51 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>סלט קיסר (TA)</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>packaging</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D19" t="n">
-        <v>147090</v>
-      </c>
       <c r="E19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F19" t="n">
+        <v>191.19</v>
+      </c>
+      <c r="G19" t="n">
         <v>120</v>
       </c>
-      <c r="F19" t="n">
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
         <v>241</v>
       </c>
-      <c r="G19" t="n">
+      <c r="J19" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="H19" t="n">
-        <v>18310</v>
-      </c>
-      <c r="I19" t="inlineStr">
+      <c r="K19" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="L19" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="n">
+      <c r="N19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -78060,38 +79642,51 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
+          <t>המבורגר (TA), קריספי ציקן (TA)</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
           <t>packaging</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D20" t="n">
-        <v>189056</v>
-      </c>
       <c r="E20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>708.45</v>
+      </c>
+      <c r="G20" t="n">
         <v>150</v>
       </c>
-      <c r="F20" t="n">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
         <v>893</v>
       </c>
-      <c r="G20" t="n">
+      <c r="J20" t="n">
         <v>29.77</v>
       </c>
-      <c r="H20" t="n">
-        <v>6351.3</v>
-      </c>
-      <c r="I20" t="inlineStr">
+      <c r="K20" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="L20" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="M20" t="n">
         <v>0</v>
       </c>
-      <c r="K20" t="n">
+      <c r="N20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -78103,38 +79698,51 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>סלט קיסר (TA)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>packaging</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D21" t="n">
-        <v>147090</v>
-      </c>
       <c r="E21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F21" t="n">
+        <v>191.19</v>
+      </c>
+      <c r="G21" t="n">
         <v>120</v>
       </c>
-      <c r="F21" t="n">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
         <v>241</v>
       </c>
-      <c r="G21" t="n">
+      <c r="J21" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="H21" t="n">
-        <v>18310</v>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="K21" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="L21" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J21" t="n">
+      <c r="M21" t="n">
         <v>0</v>
       </c>
-      <c r="K21" t="n">
+      <c r="N21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -78146,38 +79754,51 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>המבורגר, סלט קיסר, קריספי ציקן</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
           <t>packaging</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="D22" t="n">
-        <v>236146</v>
-      </c>
       <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>899.64</v>
+      </c>
+      <c r="G22" t="n">
         <v>200</v>
       </c>
-      <c r="F22" t="n">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>sun</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
         <v>1134</v>
       </c>
-      <c r="G22" t="n">
+      <c r="J22" t="n">
         <v>37.8</v>
       </c>
-      <c r="H22" t="n">
-        <v>6247.2</v>
-      </c>
-      <c r="I22" t="inlineStr">
+      <c r="K22" t="n">
+        <v>23.8</v>
+      </c>
+      <c r="L22" t="inlineStr">
         <is>
           <t>לא</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="M22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="n">
+      <c r="N22" t="n">
         <v>0</v>
       </c>
     </row>

--- a/fixi_export.xlsx
+++ b/fixi_export.xlsx
@@ -18,6 +18,7 @@
     <sheet name="מלאי ומכרזים" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="תכנית שבועית" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="הזמנה יומית" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="הזמנה לספק (לפי מכירות)" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -53,6 +54,13 @@
     <font>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="4">
@@ -85,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -96,6 +104,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1358,6 +1368,1388 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>הזמנה לספקים לפי מכירות יום 2026-04-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>מכירות: 93 מנות · הכנסה ₪5664.00 · עלות הזמנה לספקים: ₪2754.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ספק</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>פריט</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>אריזה</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>צריכה במטבח</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>יחידת מטבח</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>פחת %</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>נדרש (כולל פחת)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>כמות בחבילה</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>מס' חבילות להזמין</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>כמות בפועל שמגיעה</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>עודף (מעבר לנדרש)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>מחיר חבילה</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>סה"כ לפריט</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>מאפיית הבוקר</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>לחמניית המבורגר</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ארגז 30 יחידות</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>75</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>76.53</v>
+      </c>
+      <c r="H5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" t="n">
+        <v>90</v>
+      </c>
+      <c r="K5" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="L5" t="n">
+        <v>75</v>
+      </c>
+      <c r="M5" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ מאפיית הבוקר</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="7" t="n"/>
+      <c r="L6" s="7" t="n"/>
+      <c r="M6" s="5" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>בשר איכות בע"מ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>קציצת בקר 180 גרם</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ארגז 20 יחידות</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>47</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="H7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>60</v>
+      </c>
+      <c r="K7" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="L7" t="n">
+        <v>180</v>
+      </c>
+      <c r="M7" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ בשר איכות בע"מ</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="5" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>תנובה מוצרי חלב</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>גבינה צהובה</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>גלגל 2.5 ק"ג</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1175</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1211.34</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1288.66</v>
+      </c>
+      <c r="L9" t="n">
+        <v>200</v>
+      </c>
+      <c r="M9" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>תנובה מוצרי חלב</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>פרמזן מגוררת</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>אריזה 500 גרם</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>270</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>276.92</v>
+      </c>
+      <c r="H10" t="n">
+        <v>500</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="n">
+        <v>500</v>
+      </c>
+      <c r="K10" t="n">
+        <v>223.08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>60</v>
+      </c>
+      <c r="M10" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ תנובה מוצרי חלב</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n"/>
+      <c r="C11" s="7" t="n"/>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
+      <c r="F11" s="7" t="n"/>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="7" t="n"/>
+      <c r="I11" s="7" t="n"/>
+      <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
+      <c r="L11" s="7" t="n"/>
+      <c r="M11" s="5" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ירקות השוק</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>חסה</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ראש 300 גרם</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4740</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>12</v>
+      </c>
+      <c r="G12" t="n">
+        <v>5386.36</v>
+      </c>
+      <c r="H12" t="n">
+        <v>300</v>
+      </c>
+      <c r="I12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5400</v>
+      </c>
+      <c r="K12" t="n">
+        <v>13.64</v>
+      </c>
+      <c r="L12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ירקות השוק</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>בצל</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>שק 10 ק"ג</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>940</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>15</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1105.88</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8894.120000000001</v>
+      </c>
+      <c r="L13" t="n">
+        <v>100</v>
+      </c>
+      <c r="M13" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ירקות השוק</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>עגבנייה</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ארגז 5 ק"ג</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>3620</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>8</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3934.78</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1065.22</v>
+      </c>
+      <c r="L14" t="n">
+        <v>75</v>
+      </c>
+      <c r="M14" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ ירקות השוק</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n"/>
+      <c r="C15" s="7" t="n"/>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
+      <c r="F15" s="7" t="n"/>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="7" t="n"/>
+      <c r="I15" s="7" t="n"/>
+      <c r="J15" s="7" t="n"/>
+      <c r="K15" s="7" t="n"/>
+      <c r="L15" s="7" t="n"/>
+      <c r="M15" s="5" t="n">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>חומץ מעדנות</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>מלפפון חמוץ</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>קופסה 2.5 ק"ג</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>705</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>726.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K16" t="n">
+        <v>1773.2</v>
+      </c>
+      <c r="L16" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ חומץ מעדנות</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n"/>
+      <c r="C17" s="7" t="n"/>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
+      <c r="F17" s="7" t="n"/>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="7" t="n"/>
+      <c r="I17" s="7" t="n"/>
+      <c r="J17" s="7" t="n"/>
+      <c r="K17" s="7" t="n"/>
+      <c r="L17" s="7" t="n"/>
+      <c r="M17" s="5" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>רטבי היום</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>רוטב המבורגר</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>קופסה 1 ליטר</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>2110</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2175.26</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3000</v>
+      </c>
+      <c r="K18" t="n">
+        <v>824.74</v>
+      </c>
+      <c r="L18" t="n">
+        <v>30</v>
+      </c>
+      <c r="M18" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>רטבי היום</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>רוטב קיסר</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>קופסה 1 ליטר</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>720</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>742.27</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K19" t="n">
+        <v>257.73</v>
+      </c>
+      <c r="L19" t="n">
+        <v>40</v>
+      </c>
+      <c r="M19" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ רטבי היום</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n"/>
+      <c r="C20" s="7" t="n"/>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
+      <c r="F20" s="7" t="n"/>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="7" t="n"/>
+      <c r="I20" s="7" t="n"/>
+      <c r="J20" s="7" t="n"/>
+      <c r="K20" s="7" t="n"/>
+      <c r="L20" s="7" t="n"/>
+      <c r="M20" s="5" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>עוף עוף בע"מ</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>חזה עוף פרוס</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>ארגז 5 ק"ג</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>6360</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>6694.74</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3305.26</v>
+      </c>
+      <c r="L21" t="n">
+        <v>275</v>
+      </c>
+      <c r="M21" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ עוף עוף בע"מ</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n"/>
+      <c r="C22" s="7" t="n"/>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
+      <c r="F22" s="7" t="n"/>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="7" t="n"/>
+      <c r="I22" s="7" t="n"/>
+      <c r="J22" s="7" t="n"/>
+      <c r="K22" s="7" t="n"/>
+      <c r="L22" s="7" t="n"/>
+      <c r="M22" s="5" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>אוסם מוצרי מזון</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>פירורי לחם</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>שק 5 ק"ג</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1120</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1137.06</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3862.94</v>
+      </c>
+      <c r="L23" t="n">
+        <v>60</v>
+      </c>
+      <c r="M23" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>אוסם מוצרי מזון</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>קרוטונים</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>שק 1 ק"ג</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>450</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>459.18</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>540.8200000000001</v>
+      </c>
+      <c r="L24" t="n">
+        <v>30</v>
+      </c>
+      <c r="M24" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ אוסם מוצרי מזון</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="7" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="5" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>שמני טעם</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>שמן טיגון</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>גלון 18 ליטר</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1680</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1826.09</v>
+      </c>
+      <c r="H26" t="n">
+        <v>18000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="n">
+        <v>18000</v>
+      </c>
+      <c r="K26" t="n">
+        <v>16173.91</v>
+      </c>
+      <c r="L26" t="n">
+        <v>324</v>
+      </c>
+      <c r="M26" t="n">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ שמני טעם</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n"/>
+      <c r="C27" s="7" t="n"/>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
+      <c r="F27" s="7" t="n"/>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="7" t="n"/>
+      <c r="I27" s="7" t="n"/>
+      <c r="J27" s="7" t="n"/>
+      <c r="K27" s="7" t="n"/>
+      <c r="L27" s="7" t="n"/>
+      <c r="M27" s="5" t="n">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>אריזות השולחן</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>קופסת המבורגר קרטון</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ארגז 100 יחידות</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>34</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>34.52</v>
+      </c>
+      <c r="H28" t="n">
+        <v>100</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>100</v>
+      </c>
+      <c r="K28" t="n">
+        <v>65.48</v>
+      </c>
+      <c r="L28" t="n">
+        <v>120</v>
+      </c>
+      <c r="M28" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>אריזות השולחן</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>קופסת סלט PET</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>חבילה 50 יחידות</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>8</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G29" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>50</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>50</v>
+      </c>
+      <c r="K29" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="L29" t="n">
+        <v>75</v>
+      </c>
+      <c r="M29" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>אריזות השולחן</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>שקית נייר ניידים</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>חבילה 50 יחידות</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>42</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>42.42</v>
+      </c>
+      <c r="H30" t="n">
+        <v>50</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>50</v>
+      </c>
+      <c r="K30" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="L30" t="n">
+        <v>35</v>
+      </c>
+      <c r="M30" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>אריזות השולחן</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>מכסה לקופסת סלט</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>חבילה 50 יחידות</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>8</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>50</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>50</v>
+      </c>
+      <c r="K31" t="n">
+        <v>41.88</v>
+      </c>
+      <c r="L31" t="n">
+        <v>20</v>
+      </c>
+      <c r="M31" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ אריזות השולחן</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="n"/>
+      <c r="C32" s="7" t="n"/>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
+      <c r="F32" s="7" t="n"/>
+      <c r="G32" s="7" t="n"/>
+      <c r="H32" s="7" t="n"/>
+      <c r="I32" s="7" t="n"/>
+      <c r="J32" s="7" t="n"/>
+      <c r="K32" s="7" t="n"/>
+      <c r="L32" s="7" t="n"/>
+      <c r="M32" s="5" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>כלי חד פעמי טל</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>מזלג חד פעמי</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>חבילה 100 יחידות</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>42</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="H33" t="n">
+        <v>100</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="n">
+        <v>100</v>
+      </c>
+      <c r="K33" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="L33" t="n">
+        <v>15</v>
+      </c>
+      <c r="M33" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>כלי חד פעמי טל</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>סכין חד פעמי</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>חבילה 100 יחידות</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>42</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G34" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="H34" t="n">
+        <v>100</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1</v>
+      </c>
+      <c r="J34" t="n">
+        <v>100</v>
+      </c>
+      <c r="K34" t="n">
+        <v>57.79</v>
+      </c>
+      <c r="L34" t="n">
+        <v>15</v>
+      </c>
+      <c r="M34" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>כלי חד פעמי טל</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>מפית נייר</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>חבילה 200 יחידות</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>186</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" t="n">
+        <v>187.88</v>
+      </c>
+      <c r="H35" t="n">
+        <v>200</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="n">
+        <v>200</v>
+      </c>
+      <c r="K35" t="n">
+        <v>12.12</v>
+      </c>
+      <c r="L35" t="n">
+        <v>10</v>
+      </c>
+      <c r="M35" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ כלי חד פעמי טל</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n"/>
+      <c r="C36" s="7" t="n"/>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
+      <c r="F36" s="7" t="n"/>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="7" t="n"/>
+      <c r="I36" s="7" t="n"/>
+      <c r="J36" s="7" t="n"/>
+      <c r="K36" s="7" t="n"/>
+      <c r="L36" s="7" t="n"/>
+      <c r="M36" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>סה"כ כללי</t>
+        </is>
+      </c>
+      <c r="M38" s="9" t="n">
+        <v>2754.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/fixi_export.xlsx
+++ b/fixi_export.xlsx
@@ -19,6 +19,7 @@
     <sheet name="תכנית שבועית" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="הזמנה יומית" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="הזמנה לספק (לפי מכירות)" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="הזמנה לספק - המבורגר בלבד" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2750,6 +2751,933 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>הזמנה לספקים לפי מכירות יום 2026-04-23 - המבורגר בלבד</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="8" t="inlineStr">
+        <is>
+          <t>מכירות: 47 מנות · הכנסה ₪3040.00 · עלות הזמנה לספקים: ₪1406.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>ספק</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>פריט</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>אריזה</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>צריכה במטבח</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>יחידת מטבח</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>פחת %</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>נדרש (כולל פחת)</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>כמות בחבילה</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>מס' חבילות להזמין</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>כמות בפועל שמגיעה</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>עודף (מעבר לנדרש)</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>מחיר חבילה</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>סה"כ לפריט</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>מאפיית הבוקר</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>לחמניית המבורגר</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ארגז 30 יחידות</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>47</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>47.96</v>
+      </c>
+      <c r="H5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>60</v>
+      </c>
+      <c r="K5" t="n">
+        <v>12.04</v>
+      </c>
+      <c r="L5" t="n">
+        <v>75</v>
+      </c>
+      <c r="M5" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ מאפיית הבוקר</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="n"/>
+      <c r="C6" s="7" t="n"/>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
+      <c r="F6" s="7" t="n"/>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="7" t="n"/>
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="n"/>
+      <c r="K6" s="7" t="n"/>
+      <c r="L6" s="7" t="n"/>
+      <c r="M6" s="5" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>בשר איכות בע"מ</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>קציצת בקר 180 גרם</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ארגז 20 יחידות</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>47</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="H7" t="n">
+        <v>20</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>60</v>
+      </c>
+      <c r="K7" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="L7" t="n">
+        <v>180</v>
+      </c>
+      <c r="M7" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ בשר איכות בע"מ</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n"/>
+      <c r="C8" s="7" t="n"/>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
+      <c r="F8" s="7" t="n"/>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="7" t="n"/>
+      <c r="I8" s="7" t="n"/>
+      <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
+      <c r="L8" s="7" t="n"/>
+      <c r="M8" s="5" t="n">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>תנובה מוצרי חלב</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>גבינה צהובה</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>גלגל 2.5 ק"ג</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1175</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>3</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1211.34</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1288.66</v>
+      </c>
+      <c r="L9" t="n">
+        <v>200</v>
+      </c>
+      <c r="M9" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ תנובה מוצרי חלב</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n"/>
+      <c r="C10" s="7" t="n"/>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
+      <c r="F10" s="7" t="n"/>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="7" t="n"/>
+      <c r="I10" s="7" t="n"/>
+      <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
+      <c r="L10" s="7" t="n"/>
+      <c r="M10" s="5" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ירקות השוק</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>בצל</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>שק 10 ק"ג</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>940</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1105.88</v>
+      </c>
+      <c r="H11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>10000</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8894.120000000001</v>
+      </c>
+      <c r="L11" t="n">
+        <v>100</v>
+      </c>
+      <c r="M11" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ירקות השוק</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>עגבנייה</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ארגז 5 ק"ג</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1880</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>8</v>
+      </c>
+      <c r="G12" t="n">
+        <v>2043.48</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2956.52</v>
+      </c>
+      <c r="L12" t="n">
+        <v>75</v>
+      </c>
+      <c r="M12" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ירקות השוק</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>חסה</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ראש 300 גרם</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>940</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1068.18</v>
+      </c>
+      <c r="H13" t="n">
+        <v>300</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1200</v>
+      </c>
+      <c r="K13" t="n">
+        <v>131.82</v>
+      </c>
+      <c r="L13" t="n">
+        <v>6</v>
+      </c>
+      <c r="M13" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ ירקות השוק</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n"/>
+      <c r="C14" s="7" t="n"/>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
+      <c r="F14" s="7" t="n"/>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="7" t="n"/>
+      <c r="I14" s="7" t="n"/>
+      <c r="J14" s="7" t="n"/>
+      <c r="K14" s="7" t="n"/>
+      <c r="L14" s="7" t="n"/>
+      <c r="M14" s="5" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>חומץ מעדנות</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>מלפפון חמוץ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>קופסה 2.5 ק"ג</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>705</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>gram</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>726.8</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2500</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1773.2</v>
+      </c>
+      <c r="L15" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ חומץ מעדנות</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n"/>
+      <c r="C16" s="7" t="n"/>
+      <c r="D16" s="7" t="n"/>
+      <c r="E16" s="7" t="n"/>
+      <c r="F16" s="7" t="n"/>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="7" t="n"/>
+      <c r="I16" s="7" t="n"/>
+      <c r="J16" s="7" t="n"/>
+      <c r="K16" s="7" t="n"/>
+      <c r="L16" s="7" t="n"/>
+      <c r="M16" s="5" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>רטבי היום</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>רוטב המבורגר</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>קופסה 1 ליטר</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1410</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1453.61</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K17" t="n">
+        <v>546.39</v>
+      </c>
+      <c r="L17" t="n">
+        <v>30</v>
+      </c>
+      <c r="M17" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ רטבי היום</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n"/>
+      <c r="C18" s="7" t="n"/>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
+      <c r="F18" s="7" t="n"/>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="7" t="n"/>
+      <c r="I18" s="7" t="n"/>
+      <c r="J18" s="7" t="n"/>
+      <c r="K18" s="7" t="n"/>
+      <c r="L18" s="7" t="n"/>
+      <c r="M18" s="5" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>אריזות השולחן</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>קופסת המבורגר קרטון</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ארגז 100 יחידות</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>21</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>21.32</v>
+      </c>
+      <c r="H19" t="n">
+        <v>100</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>100</v>
+      </c>
+      <c r="K19" t="n">
+        <v>78.68000000000001</v>
+      </c>
+      <c r="L19" t="n">
+        <v>120</v>
+      </c>
+      <c r="M19" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>אריזות השולחן</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>שקית נייר ניידים</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>חבילה 50 יחידות</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>21</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="H20" t="n">
+        <v>50</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>50</v>
+      </c>
+      <c r="K20" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="L20" t="n">
+        <v>35</v>
+      </c>
+      <c r="M20" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ אריזות השולחן</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="7" t="n"/>
+      <c r="I21" s="7" t="n"/>
+      <c r="J21" s="7" t="n"/>
+      <c r="K21" s="7" t="n"/>
+      <c r="L21" s="7" t="n"/>
+      <c r="M21" s="5" t="n">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>כלי חד פעמי טל</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>מזלג חד פעמי</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>חבילה 100 יחידות</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>21</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="H22" t="n">
+        <v>100</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>100</v>
+      </c>
+      <c r="K22" t="n">
+        <v>78.89</v>
+      </c>
+      <c r="L22" t="n">
+        <v>15</v>
+      </c>
+      <c r="M22" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>כלי חד פעמי טל</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>סכין חד פעמי</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>חבילה 100 יחידות</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>21</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>21.11</v>
+      </c>
+      <c r="H23" t="n">
+        <v>100</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>100</v>
+      </c>
+      <c r="K23" t="n">
+        <v>78.89</v>
+      </c>
+      <c r="L23" t="n">
+        <v>15</v>
+      </c>
+      <c r="M23" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>כלי חד פעמי טל</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>מפית נייר</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>חבילה 200 יחידות</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>94</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>94.95</v>
+      </c>
+      <c r="H24" t="n">
+        <v>200</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>200</v>
+      </c>
+      <c r="K24" t="n">
+        <v>105.05</v>
+      </c>
+      <c r="L24" t="n">
+        <v>10</v>
+      </c>
+      <c r="M24" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>סה"כ כלי חד פעמי טל</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
+      <c r="F25" s="7" t="n"/>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="7" t="n"/>
+      <c r="I25" s="7" t="n"/>
+      <c r="J25" s="7" t="n"/>
+      <c r="K25" s="7" t="n"/>
+      <c r="L25" s="7" t="n"/>
+      <c r="M25" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>סה"כ כללי</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>1406.5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
